--- a/reports/jobs_2026-10-24.xlsx
+++ b/reports/jobs_2026-10-24.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I111"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1049,17 +1049,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Arm India</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Theorem Proving Engineer</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27443</t>
+          <t>https://careers.arm.com/job/austin/theorem-proving-engineer/33099/97584421536</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://careers.arm.com/</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1092,17 +1092,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Arm India</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Application Development Engineer</t>
+          <t>Compiler Engineer (Machine Learning)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1110,11 +1110,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -1122,12 +1118,12 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26833</t>
+          <t>https://careers.arm.com/job/lund/compiler-engineer-machine-learning/33099/94847322016</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://careers.arm.com/</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1144,12 +1140,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Principle Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1157,11 +1153,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -1169,7 +1161,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27455</t>
+          <t>https://www.atlassian.com/company/careers/details/27443</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1191,12 +1183,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Application Development Engineer</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1216,7 +1208,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25539</t>
+          <t>https://www.atlassian.com/company/careers/details/26833</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1238,12 +1230,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Principle Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1253,7 +1245,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Remote or Remote</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1263,7 +1255,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25283</t>
+          <t>https://www.atlassian.com/company/careers/details/27455</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1285,12 +1277,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,7 +1302,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25561</t>
+          <t>https://www.atlassian.com/company/careers/details/25539</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1332,12 +1324,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Principle Machine Learning Systems Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1347,7 +1339,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote or Remote</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1357,7 +1349,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27796</t>
+          <t>https://www.atlassian.com/company/careers/details/25283</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1379,12 +1371,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1392,7 +1384,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -1400,7 +1396,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26758</t>
+          <t>https://www.atlassian.com/company/careers/details/25561</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1422,12 +1418,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Principle Machine Learning Systems Engineer</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1447,7 +1443,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25538</t>
+          <t>https://www.atlassian.com/company/careers/details/27796</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1469,12 +1465,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1482,11 +1478,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -1494,7 +1486,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27794</t>
+          <t>https://www.atlassian.com/company/careers/details/26758</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1516,12 +1508,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1541,7 +1533,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25566</t>
+          <t>https://www.atlassian.com/company/careers/details/25538</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1563,12 +1555,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack (Loom Billing &amp; Integrations)</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1588,7 +1580,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27431</t>
+          <t>https://www.atlassian.com/company/careers/details/27794</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1610,12 +1602,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning System Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1635,7 +1627,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27388</t>
+          <t>https://www.atlassian.com/company/careers/details/25566</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1657,12 +1649,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>EMEA Field CTO, DX — Engineering Executive Advisor</t>
+          <t>Software Engineer – Full Stack (Loom Billing &amp; Integrations)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1682,7 +1674,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/24899</t>
+          <t>https://www.atlassian.com/company/careers/details/27431</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1704,12 +1696,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, 2027 Graduate Canada</t>
+          <t>Machine Learning System Engineer</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1717,7 +1709,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -1725,7 +1721,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26070</t>
+          <t>https://www.atlassian.com/company/careers/details/27388</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1747,12 +1743,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, 2027 Graduate U.S.</t>
+          <t>EMEA Field CTO, DX — Engineering Executive Advisor</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1760,7 +1756,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25999</t>
+          <t>https://www.atlassian.com/company/careers/details/24899</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Data Engineer, 2027 Graduate U.S</t>
+          <t>Software Engineer, 2027 Graduate Canada</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25998</t>
+          <t>https://www.atlassian.com/company/careers/details/26070</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1833,12 +1833,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, 2027 Graduate U.S.</t>
+          <t>Machine Learning Engineer, 2027 Graduate U.S.</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25813</t>
+          <t>https://www.atlassian.com/company/careers/details/25999</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1876,12 +1876,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, 2027 Canada</t>
+          <t>Data Engineer, 2027 Graduate U.S</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26275</t>
+          <t>https://www.atlassian.com/company/careers/details/25998</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Data Engineer Intern, 2027 Summer U.S.</t>
+          <t>Software Engineer, 2027 Graduate U.S.</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1932,11 +1932,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -1944,7 +1940,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26272</t>
+          <t>https://www.atlassian.com/company/careers/details/25813</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1966,7 +1962,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Research Intern, 2027 Summer U.S.</t>
+          <t>Software Engineer Intern, 2027 Canada</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1987,7 +1983,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26270</t>
+          <t>https://www.atlassian.com/company/careers/details/26275</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2009,12 +2005,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Intern, 2027 Summer U.S.</t>
+          <t>Data Engineer Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2022,7 +2018,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26268</t>
+          <t>https://www.atlassian.com/company/careers/details/26272</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Security Engineer Intern, 2027 Summer U.S.</t>
+          <t>Research Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26267</t>
+          <t>https://www.atlassian.com/company/careers/details/26270</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2095,12 +2095,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, 2027 Summer U.S.</t>
+          <t>Machine Learning Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26266</t>
+          <t>https://www.atlassian.com/company/careers/details/26268</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Product Design Intern, 2027 Summer U.S.</t>
+          <t>Security Engineer Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2151,11 +2151,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -2163,7 +2159,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26273</t>
+          <t>https://www.atlassian.com/company/careers/details/26267</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2185,7 +2181,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Product Management Intern, 2027 Summer U.S.</t>
+          <t>Software Engineer Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2198,11 +2194,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -2210,7 +2202,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26274</t>
+          <t>https://www.atlassian.com/company/careers/details/26266</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2232,7 +2224,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>AI Demand Intelligence Intern, 2027 Summer U.S.</t>
+          <t>Product Design Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2257,7 +2249,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26843</t>
+          <t>https://www.atlassian.com/company/careers/details/26273</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2279,12 +2271,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Security Engineer</t>
+          <t>Product Management Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2304,7 +2296,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27275</t>
+          <t>https://www.atlassian.com/company/careers/details/26274</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2326,12 +2318,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Security Engineer</t>
+          <t>AI Demand Intelligence Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2351,7 +2343,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26986</t>
+          <t>https://www.atlassian.com/company/careers/details/26843</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2373,12 +2365,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Security Testing Engineer - Penetration Tester</t>
+          <t>Enterprise Security Engineer</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2388,7 +2380,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Remote or Remote</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2398,7 +2390,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26643</t>
+          <t>https://www.atlassian.com/company/careers/details/27275</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2415,12 +2407,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Chargebee</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CEO AI billing software built for founders who ship fast</t>
+          <t>Enterprise Security Engineer</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2433,7 +2425,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -2441,12 +2437,12 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/ceo/</t>
+          <t>https://www.atlassian.com/company/careers/details/26986</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/careers/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2458,17 +2454,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Chargebee</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Product Launch and price new features without waiting on engineering</t>
+          <t>Security Testing Engineer - Penetration Tester</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2476,7 +2472,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Remote or Remote</t>
+        </is>
+      </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/product/</t>
+          <t>https://www.atlassian.com/company/careers/details/26643</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/careers/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Growth Test offers, run promotions and lift conversion</t>
+          <t>CEO AI billing software built for founders who ship fast</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/growth/</t>
+          <t>https://www.chargebee.com/solutions/role/ceo/</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2544,12 +2544,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Chargebee</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Implementation Engineer 2</t>
+          <t>Product Launch and price new features without waiting on engineering</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2562,11 +2562,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -2574,12 +2570,12 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
+          <t>https://www.chargebee.com/solutions/role/product/</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.chargebee.com/careers/</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2591,17 +2587,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Chargebee</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
+          <t>Growth Test offers, run promotions and lift conversion</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2609,11 +2605,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>India Full-time</t>
-        </is>
-      </c>
+      <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -2621,12 +2613,12 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
+          <t>https://www.chargebee.com/solutions/role/growth/</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.chargebee.com/careers/</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2638,17 +2630,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer-3</t>
+          <t>Gen AI Engineer-AWS</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2656,11 +2648,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -2668,12 +2656,12 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
+          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Gen-AI-Engineer-AWS_SR-47131</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2685,17 +2673,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Integration &amp; Customization Engineer -1</t>
+          <t>CPGR Growth Leader, AI Engineering, Strategic Accounts</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2703,11 +2691,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>India Full-time</t>
-        </is>
-      </c>
+      <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -2715,12 +2699,12 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
+          <t>https://fractal.ai/en-US/Careers/job/New-York/CPGR-Growth-Leader--AI-Engineering--Strategic-Accounts_SR-46966</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2732,17 +2716,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
+          <t>Data Engineer - AWS</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2758,12 +2742,12 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
+          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Data-Engineer---AWS_SR-37522</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2775,12 +2759,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Implementation Engineer</t>
+          <t>GenAI-Engineer</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2793,11 +2777,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -2805,12 +2785,12 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-710627-implementation-engineer</t>
+          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/GenAI-Engineer_SR-46807</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2822,12 +2802,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Billing)</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2840,11 +2820,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -2852,12 +2828,12 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-700106-software-engineer-2-billing</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2869,17 +2845,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - 3 (Voice)</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2887,11 +2863,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -2899,12 +2871,12 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2916,12 +2888,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 2</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2934,11 +2906,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -2946,12 +2914,12 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2963,17 +2931,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 3</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2983,7 +2951,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bengaluru-VTP, India</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -2993,12 +2961,12 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3010,12 +2978,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Product Head, Voice AI</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3030,7 +2998,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -3040,12 +3008,12 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -3057,17 +3025,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Software Developer - 3 (Voice4Ai-Backend)</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3077,7 +3045,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>New Delhi, in</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3087,12 +3055,12 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-voice4aibackend</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -3104,17 +3072,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Voicebot)</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3124,7 +3092,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -3134,12 +3102,12 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -3151,17 +3119,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3169,11 +3137,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -3181,12 +3145,12 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3198,17 +3162,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Gen AI Engineer-AWS</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3224,12 +3188,12 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Gen-AI-Engineer-AWS_SR-47131</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -3241,17 +3205,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>CPGR Growth Leader, AI Engineering, Strategic Accounts</t>
+          <t>Cluster Head- Last mile - Chennai</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3259,7 +3223,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu</t>
+        </is>
+      </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -3267,12 +3235,12 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-York/CPGR-Growth-Leader--AI-Engineering--Strategic-Accounts_SR-46966</t>
+          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3284,17 +3252,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS</t>
+          <t>Trainee - Recruitment Coordinator</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3302,7 +3270,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -3310,12 +3282,12 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Data-Engineer---AWS_SR-37522</t>
+          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -3327,12 +3299,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>GenAI-Engineer</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3353,12 +3325,12 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/GenAI-Engineer_SR-46807</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3370,12 +3342,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>Engineer 3 - Business Systems</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3388,7 +3360,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -3396,12 +3372,12 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -3413,17 +3389,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3439,12 +3415,12 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3456,12 +3432,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Open Financial</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>We’re hiring Build with us Roles across engineering, product and GTM.</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3482,12 +3458,12 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://open.money/company/careers</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://open.money/careers</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3499,12 +3475,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3517,11 +3493,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru-VTP, India</t>
-        </is>
-      </c>
+      <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -3529,12 +3501,12 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3546,17 +3518,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Intern - Talent Acquisition</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3566,7 +3538,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Gurugram, Haryana</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -3576,12 +3548,12 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3593,17 +3565,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3613,7 +3585,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>New Delhi, in</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -3623,12 +3595,12 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -3640,17 +3612,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Internship - Talent Acquisition</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3660,7 +3632,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -3670,12 +3642,12 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -3687,12 +3659,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Talent Acquisition Intern</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -3705,7 +3677,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -3713,12 +3689,12 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://jobs.lever.co/paytm/6d7551f7-34c3-46a2-a4e4-18b29f15338c</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -3730,17 +3706,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Talent Acquisition Intern - Bangalore</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3748,7 +3724,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -3756,12 +3736,12 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -3773,17 +3753,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Cluster Head- Last mile - Chennai</t>
+          <t>Talent Acquisition Intern - IT Recruitment</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3793,7 +3773,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -3803,12 +3783,12 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
+          <t>https://jobs.lever.co/paytm/95eadc2b-27bf-40fe-b6e6-93aaeadd08f7</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -3820,12 +3800,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Trainee - Recruitment Coordinator</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -3838,11 +3818,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -3850,12 +3826,12 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -3867,17 +3843,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3885,7 +3861,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -3893,12 +3873,12 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -3910,12 +3890,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Engineer 3 - Business Systems</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -3930,7 +3910,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -3940,12 +3920,12 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -3957,17 +3937,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3975,7 +3955,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -3983,12 +3967,12 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -4000,17 +3984,17 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Open Financial</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>We’re hiring Build with us Roles across engineering, product and GTM.</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -4026,12 +4010,12 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>https://open.money/company/careers</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://open.money/careers</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -4043,12 +4027,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>ENG Project/ Program - Intern</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4061,7 +4045,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -4069,12 +4057,12 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -4086,17 +4074,17 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Intern - Talent Acquisition</t>
+          <t>Industrial Trainee</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4106,7 +4094,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Gurugram, Haryana</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -4116,12 +4104,12 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8266405?gh_jid=8266405</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -4133,17 +4121,17 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t xml:space="preserve">Security Engineer - Identity and Access </t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -4153,7 +4141,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -4163,12 +4151,12 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -4180,27 +4168,27 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Internship - Talent Acquisition</t>
+          <t>Software Engineer - Cloud: Azure</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>0-2 years</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t xml:space="preserve">Bangalore </t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -4210,12 +4198,12 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -4227,17 +4215,17 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern</t>
+          <t>Software Engineer - IAM</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -4247,7 +4235,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -4257,12 +4245,12 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/6d7551f7-34c3-46a2-a4e4-18b29f15338c</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -4274,12 +4262,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Bangalore</t>
+          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4292,11 +4280,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -4304,12 +4288,12 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzgsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -4321,17 +4305,17 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - IT Recruitment</t>
+          <t>AI Screenplay Writer</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -4339,11 +4323,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
+      <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -4351,12 +4331,12 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/95eadc2b-27bf-40fe-b6e6-93aaeadd08f7</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -4368,17 +4348,17 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Talent Acquisition- Intern || Noida ||</t>
+          <t>AI Video Editor</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -4386,11 +4366,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
+      <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -4398,12 +4374,12 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/648841ab-2778-4759-a4c9-eabae97ec65d</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -4415,12 +4391,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>AI Sound Designer</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4441,12 +4417,12 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -4458,17 +4434,17 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>AI Animator</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -4476,11 +4452,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E89" s="2" t="inlineStr"/>
       <c r="F89" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -4488,12 +4460,12 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -4505,17 +4477,17 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -4525,7 +4497,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -4535,12 +4507,12 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -4552,17 +4524,17 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -4572,7 +4544,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -4582,12 +4554,12 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -4599,12 +4571,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>SirionLabs</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>Intern- Employee Engagement</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -4625,12 +4597,12 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://www.sirion.ai/jobs/intern-employee-engagement/</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://www.sirionlabs.com/careers/</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -4642,12 +4614,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>ENG Project/ Program - Intern</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -4660,11 +4632,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="2" t="inlineStr">
         <is>
           <t>2026-10-24</t>
@@ -4672,12 +4640,12 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -4689,17 +4657,17 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Stripe India</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Industrial Trainee</t>
+          <t>Software Engineer, Intern</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -4709,7 +4677,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -4719,12 +4687,12 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8266405?gh_jid=8266405</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://boards.greenhouse.io/stripe</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -4736,12 +4704,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Unacademy</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security Engineer - Identity and Access </t>
+          <t>Test Jerin</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -4756,7 +4724,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -4766,12 +4734,12 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -4783,27 +4751,27 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Unacademy</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud: Azure</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>0-2 years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bangalore </t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -4813,12 +4781,12 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -4830,12 +4798,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Zscaler India</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - IAM</t>
+          <t>Escalation Engineer</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -4850,7 +4818,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Bangalore, IND</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -4860,12 +4828,12 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+          <t>https://job-boards.greenhouse.io/zscaler/jobs/5263563007</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://boards.greenhouse.io/zscaler</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -4874,638 +4842,8 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>Scaler</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>Remote Instructor- Python</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/careers/</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>ShareChat</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr"/>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="G99" s="3" t="inlineStr">
-        <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzgsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>https://sharechat.com/careers</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>ShareChat</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>AI Screenplay Writer</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr"/>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="G100" s="3" t="inlineStr">
-        <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>https://sharechat.com/careers</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>ShareChat</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>AI Video Editor</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr"/>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="G101" s="3" t="inlineStr">
-        <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>https://sharechat.com/careers</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>ShareChat</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>AI Sound Designer</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr"/>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="G102" s="3" t="inlineStr">
-        <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>https://sharechat.com/careers</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>ShareChat</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>AI Animator</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr"/>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="G103" s="3" t="inlineStr">
-        <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>https://sharechat.com/careers</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>Shipsy</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>QA Engineer</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>QA / SDET</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="G104" s="3" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>Shipsy</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Full Stack</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="G105" s="3" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>SirionLabs</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Intern- Employee Engagement</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr"/>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="G106" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sirion.ai/jobs/intern-employee-engagement/</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sirionlabs.com/careers/</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>Sprinklr</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>Internship and Early Careers</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr"/>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="G107" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sprinklr.com/careers/</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>Stripe India</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer, Intern</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="G108" s="3" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/stripe</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>Unacademy</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>Test Jerin</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="G109" s="3" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>Unacademy</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="G110" s="3" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>Zscaler India</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>Escalation Engineer</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore, IND</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="G111" s="3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/zscaler/jobs/5263563007</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/zscaler</t>
-        </is>
-      </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I111"/>
+  <autoFilter ref="A1:I97"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -5603,20 +4941,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId110"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5628,7 +4952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5676,15 +5000,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Exotel</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://exotel.com/careers/</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://exotel.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>INDmoney</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>https://www.indmoney.com/careers</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5693,18 +5037,18 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Log9 Materials</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>https://www.log9materials.com/careers</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5713,18 +5057,18 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Signzy</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://www.signzy.com/careers/</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5733,18 +5077,38 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Blinkit</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://blinkit.com/careers</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://blinkit.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5753,38 +5117,38 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Blinkit</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://blinkit.com/careers</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Capillary Technologies</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://www.capillarytech.com/careers/</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
-  - navigating to "https://blinkit.com/careers", waiting until "networkidle"
+  - navigating to "https://www.capillarytech.com/careers/", waiting until "networkidle"
 </t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>CRED</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://careers.cred.club/</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5793,38 +5157,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Capillary Technologies</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://www.capillarytech.com/careers/</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.capillarytech.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Cleartrip</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://www.cleartrip.com/careers</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5833,18 +5177,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Nykaa</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -5853,18 +5197,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5873,18 +5217,38 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LatentView Analytics</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://www.latentview.com/careers/</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.latentview.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5893,38 +5257,38 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>OYO</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>https://www.oyorooms.com/careers/</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FirstCry</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://www.firstcry.com/careers</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
-  - navigating to "https://www.oyorooms.com/careers/", waiting until "networkidle"
+  - navigating to "https://www.firstcry.com/careers", waiting until "networkidle"
 </t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -5933,18 +5297,18 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Swiggy</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>https://careers.swiggy.com/</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5953,18 +5317,18 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -5973,18 +5337,18 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -5993,18 +5357,18 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
